--- a/data/Processed/Participant_details.xlsx
+++ b/data/Processed/Participant_details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ecf-exp2-notif-mmn\data\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418E47D9-1405-456B-B802-892A58895DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EA0A75-C75B-4553-A416-88BC7AB2CE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33120" yWindow="1305" windowWidth="21600" windowHeight="11385" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="65">
   <si>
     <t>SN</t>
   </si>
@@ -210,6 +210,30 @@
   </si>
   <si>
     <t>non_acd</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>SD041</t>
+  </si>
+  <si>
+    <t>SD042</t>
+  </si>
+  <si>
+    <t>SD043</t>
+  </si>
+  <si>
+    <t>SD044</t>
+  </si>
+  <si>
+    <t>SD045</t>
+  </si>
+  <si>
+    <t>SD046</t>
+  </si>
+  <si>
+    <t>SD047</t>
   </si>
 </sst>
 </file>
@@ -590,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865CEB74-C7CC-4BC7-8922-8A1352A31C27}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
@@ -1533,7 +1557,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1541,7 +1565,7 @@
         <v>36</v>
       </c>
       <c r="C33" s="1">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>45</v>
@@ -1561,8 +1585,11 @@
       <c r="I33" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L33" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1570,7 +1597,7 @@
         <v>37</v>
       </c>
       <c r="C34" s="1">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>45</v>
@@ -1591,7 +1618,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1620,7 +1647,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1649,7 +1676,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1678,7 +1705,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1707,7 +1734,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1736,7 +1763,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1763,6 +1790,209 @@
       </c>
       <c r="I40" s="1" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="1">
+        <v>34</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G41" s="1">
+        <v>156</v>
+      </c>
+      <c r="H41" s="1">
+        <v>143</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="1">
+        <v>38</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" s="1">
+        <v>156</v>
+      </c>
+      <c r="H42" s="1">
+        <v>140</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="1">
+        <v>28</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G43" s="1">
+        <v>110</v>
+      </c>
+      <c r="H43" s="1">
+        <v>103</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="1">
+        <v>26</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G44" s="1">
+        <v>124</v>
+      </c>
+      <c r="H44" s="1">
+        <v>91</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="1">
+        <v>26</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G45" s="1">
+        <v>152</v>
+      </c>
+      <c r="H45" s="1">
+        <v>101</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="1">
+        <v>23</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G46" s="1">
+        <v>102</v>
+      </c>
+      <c r="H46" s="1">
+        <v>76</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="1">
+        <v>26</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G47" s="1">
+        <v>128</v>
+      </c>
+      <c r="H47" s="1">
+        <v>105</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/Processed/Participant_details.xlsx
+++ b/data/Processed/Participant_details.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ecf-exp2-notif-mmn\data\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EA0A75-C75B-4553-A416-88BC7AB2CE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324E80BA-93D5-47F3-B250-9796698D38E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="91">
   <si>
     <t>SN</t>
   </si>
@@ -50,9 +50,6 @@
     <t xml:space="preserve">Age </t>
   </si>
   <si>
-    <t>Data collection location</t>
-  </si>
-  <si>
     <t>sub002</t>
   </si>
   <si>
@@ -234,6 +231,87 @@
   </si>
   <si>
     <t>SD047</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>B1_deviant</t>
+  </si>
+  <si>
+    <t>B2_deviant</t>
+  </si>
+  <si>
+    <t>B3_deviant</t>
+  </si>
+  <si>
+    <t>SD048</t>
+  </si>
+  <si>
+    <t>SD049</t>
+  </si>
+  <si>
+    <t>SD050</t>
+  </si>
+  <si>
+    <t>SD051</t>
+  </si>
+  <si>
+    <t>SD052</t>
+  </si>
+  <si>
+    <t>SD053</t>
+  </si>
+  <si>
+    <t>SD054</t>
+  </si>
+  <si>
+    <t>SD055</t>
+  </si>
+  <si>
+    <t>SD056</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>SD057</t>
+  </si>
+  <si>
+    <t>SD058</t>
+  </si>
+  <si>
+    <t>SD059</t>
+  </si>
+  <si>
+    <t>SD060</t>
+  </si>
+  <si>
+    <t>SD061</t>
+  </si>
+  <si>
+    <t>PN</t>
+  </si>
+  <si>
+    <t>BT</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>SD062</t>
+  </si>
+  <si>
+    <t>SD063</t>
+  </si>
+  <si>
+    <t>SD064</t>
+  </si>
+  <si>
+    <t>SD065</t>
+  </si>
+  <si>
+    <t>SD066</t>
   </si>
 </sst>
 </file>
@@ -614,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865CEB74-C7CC-4BC7-8922-8A1352A31C27}">
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
@@ -626,10 +704,13 @@
     <col min="7" max="7" width="23.42578125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="17.5703125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="17.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -640,42 +721,51 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1">
         <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2" s="1">
         <v>60</v>
@@ -684,27 +774,33 @@
         <v>50</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
         <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3" s="1">
         <v>176</v>
@@ -713,27 +809,33 @@
         <v>130</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1">
         <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4" s="1">
         <v>124</v>
@@ -742,27 +844,33 @@
         <v>107</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5" s="1">
         <v>140</v>
@@ -771,27 +879,33 @@
         <v>104</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1">
         <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6" s="1">
         <v>107</v>
@@ -800,27 +914,33 @@
         <v>60</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1">
         <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7" s="1">
         <v>167</v>
@@ -829,27 +949,33 @@
         <v>124</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1">
         <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1">
         <v>141</v>
@@ -858,27 +984,33 @@
         <v>85</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9" s="1">
         <v>78</v>
@@ -887,27 +1019,33 @@
         <v>67</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1">
         <v>26</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10" s="1">
         <v>85</v>
@@ -916,27 +1054,33 @@
         <v>59</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G11" s="1">
         <v>157</v>
@@ -945,27 +1089,33 @@
         <v>91</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1">
         <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G12" s="1">
         <v>110</v>
@@ -974,27 +1124,33 @@
         <v>76</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1">
         <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G13" s="1">
         <v>162</v>
@@ -1003,27 +1159,33 @@
         <v>102</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1">
         <v>28</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G14" s="1">
         <v>101</v>
@@ -1032,27 +1194,33 @@
         <v>88</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1">
         <v>31</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G15" s="1">
         <v>158</v>
@@ -1061,27 +1229,33 @@
         <v>119</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1">
         <v>28</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G16" s="1">
         <v>179</v>
@@ -1090,27 +1264,33 @@
         <v>137</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1">
         <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G17" s="1">
         <v>88</v>
@@ -1119,27 +1299,33 @@
         <v>66</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1">
         <v>28</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G18" s="1">
         <v>145</v>
@@ -1148,27 +1334,33 @@
         <v>113</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="1">
         <v>25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G19" s="1">
         <v>106</v>
@@ -1177,27 +1369,36 @@
         <v>78</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="1">
         <v>26</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G20" s="1">
         <v>128</v>
@@ -1206,27 +1407,33 @@
         <v>107</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="1">
         <v>25</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G21" s="1">
         <v>134</v>
@@ -1235,27 +1442,33 @@
         <v>92</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1">
         <v>20</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G22" s="1">
         <v>146</v>
@@ -1264,27 +1477,33 @@
         <v>119</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G23" s="1">
         <v>131</v>
@@ -1293,27 +1512,33 @@
         <v>98</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1">
         <v>22</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G24" s="1">
         <v>112</v>
@@ -1322,27 +1547,33 @@
         <v>98</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="1">
         <v>19</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G25" s="1">
         <v>156</v>
@@ -1351,27 +1582,33 @@
         <v>96</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1">
         <v>18</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G26" s="1">
         <v>144</v>
@@ -1380,27 +1617,33 @@
         <v>111</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="1">
         <v>21</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" s="1">
         <v>83</v>
@@ -1409,27 +1652,33 @@
         <v>89</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="1">
         <v>18</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G28" s="1">
         <v>198</v>
@@ -1438,27 +1687,33 @@
         <v>126</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1">
         <v>21</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G29" s="1">
         <v>185</v>
@@ -1467,27 +1722,33 @@
         <v>127</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" s="1">
         <v>21</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G30" s="1">
         <v>155</v>
@@ -1496,27 +1757,33 @@
         <v>119</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="1">
         <v>21</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G31" s="1">
         <v>135</v>
@@ -1525,27 +1792,33 @@
         <v>98</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="1">
         <v>22</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G32" s="1">
         <v>111</v>
@@ -1554,7 +1827,13 @@
         <v>51</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -1562,19 +1841,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="1">
         <v>36</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G33" s="1">
         <v>143</v>
@@ -1583,10 +1862,16 @@
         <v>128</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -1594,19 +1879,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34" s="1">
         <v>27</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G34" s="1">
         <v>166</v>
@@ -1615,7 +1900,13 @@
         <v>116</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -1623,19 +1914,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" s="1">
         <v>28</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G35" s="1">
         <v>230</v>
@@ -1644,7 +1935,16 @@
         <v>161</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -1652,19 +1952,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36" s="1">
         <v>34</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G36" s="1">
         <v>157</v>
@@ -1673,7 +1973,16 @@
         <v>115</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -1681,19 +1990,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="1">
         <v>26</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G37" s="1">
         <v>130</v>
@@ -1702,7 +2011,16 @@
         <v>141</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -1710,19 +2028,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" s="1">
         <v>25</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G38" s="1">
         <v>209</v>
@@ -1731,7 +2049,16 @@
         <v>153</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -1739,19 +2066,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="1">
         <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G39" s="1">
         <v>172</v>
@@ -1760,7 +2087,16 @@
         <v>159</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -1768,19 +2104,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" s="1">
         <v>31</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G40" s="1">
         <v>164</v>
@@ -1789,7 +2125,16 @@
         <v>121</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -1797,19 +2142,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="1">
         <v>34</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G41" s="1">
         <v>156</v>
@@ -1818,7 +2163,16 @@
         <v>143</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -1826,19 +2180,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42" s="1">
         <v>38</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G42" s="1">
         <v>156</v>
@@ -1847,7 +2201,16 @@
         <v>140</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -1855,19 +2218,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C43" s="1">
         <v>28</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G43" s="1">
         <v>110</v>
@@ -1876,7 +2239,16 @@
         <v>103</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -1884,19 +2256,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C44" s="1">
         <v>26</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G44" s="1">
         <v>124</v>
@@ -1905,7 +2277,16 @@
         <v>91</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -1913,19 +2294,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C45" s="1">
         <v>26</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G45" s="1">
         <v>152</v>
@@ -1934,7 +2315,16 @@
         <v>101</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -1942,19 +2332,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C46" s="1">
         <v>23</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G46" s="1">
         <v>102</v>
@@ -1964,6 +2354,15 @@
       </c>
       <c r="I46" s="1" t="s">
         <v>54</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -1971,19 +2370,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C47" s="1">
         <v>26</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G47" s="1">
         <v>128</v>
@@ -1992,11 +2391,622 @@
         <v>105</v>
       </c>
       <c r="I47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="1">
+        <v>22</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" s="1">
+        <v>169</v>
+      </c>
+      <c r="H48" s="1">
+        <v>97</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="J48" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="1">
+        <v>22</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G49" s="1">
+        <v>137</v>
+      </c>
+      <c r="H49" s="1">
+        <v>114</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="1">
+        <v>21</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G50" s="1">
+        <v>163</v>
+      </c>
+      <c r="H50" s="1">
+        <v>138</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="1">
+        <v>23</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G51" s="1">
+        <v>145</v>
+      </c>
+      <c r="H51" s="1">
+        <v>117</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" s="1">
+        <v>24</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G52" s="1">
+        <v>97</v>
+      </c>
+      <c r="H52" s="1">
+        <v>84</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="1">
+        <v>23</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G53" s="1">
+        <v>82</v>
+      </c>
+      <c r="H53" s="1">
+        <v>80</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="1">
+        <v>23</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G54" s="1">
+        <v>177</v>
+      </c>
+      <c r="H54" s="1">
+        <v>143</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="1">
+        <v>48</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" s="1">
+        <v>131</v>
+      </c>
+      <c r="H55" s="1">
+        <v>110</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="1">
+        <v>24</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G56" s="1">
+        <v>158</v>
+      </c>
+      <c r="H56" s="1">
+        <v>137</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" s="1">
+        <v>20</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G57" s="1">
+        <v>140</v>
+      </c>
+      <c r="H57" s="1">
+        <v>101</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" s="1">
+        <v>26</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G58" s="1">
+        <v>151</v>
+      </c>
+      <c r="H58" s="1">
+        <v>112</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" s="1">
+        <v>20</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G59" s="1">
+        <v>191</v>
+      </c>
+      <c r="H59" s="1">
+        <v>154</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="1">
+        <v>30</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G60" s="1">
+        <v>147</v>
+      </c>
+      <c r="H60" s="1">
+        <v>98</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" s="1">
+        <v>21</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G61" s="1">
+        <v>96</v>
+      </c>
+      <c r="H61" s="1">
+        <v>98</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I41" xr:uid="{865CEB74-C7CC-4BC7-8922-8A1352A31C27}"/>
+  <autoFilter ref="A1:I61" xr:uid="{865CEB74-C7CC-4BC7-8922-8A1352A31C27}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Processed/Participant_details.xlsx
+++ b/data/Processed/Participant_details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ecf-exp2-notif-mmn\data\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAF40C1-D319-4EFD-B12A-651F9BFBFA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B0A7BB-ED02-459A-8BC9-90521C93D020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="78">
   <si>
     <t>gender</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>b3_deviant</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>Indivisual  SN  ERP not good</t>
   </si>
 </sst>
 </file>
@@ -647,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865CEB74-C7CC-4BC7-8922-8A1352A31C27}">
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="1" customWidth="1"/>
@@ -657,11 +663,12 @@
     <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="8" width="22.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
@@ -686,8 +693,11 @@
       <c r="H1" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -710,7 +720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -733,7 +743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -756,7 +766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -779,7 +789,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -802,7 +812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -825,7 +835,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -848,7 +858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -871,7 +881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -894,7 +904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -917,7 +927,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -940,7 +950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -963,7 +973,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -986,7 +996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
@@ -1009,7 +1019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -1840,7 +1850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>61</v>
       </c>
@@ -1866,7 +1876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>62</v>
       </c>
@@ -1892,7 +1902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>63</v>
       </c>
@@ -1918,7 +1928,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>64</v>
       </c>
@@ -1944,7 +1954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>65</v>
       </c>
@@ -1970,7 +1980,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>66</v>
       </c>
@@ -1996,7 +2006,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>67</v>
       </c>
@@ -2022,7 +2032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>68</v>
       </c>
@@ -2047,8 +2057,11 @@
       <c r="H56" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I56" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>69</v>
       </c>
@@ -2074,7 +2087,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>70</v>
       </c>

--- a/data/Processed/Participant_details.xlsx
+++ b/data/Processed/Participant_details.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ecf-exp2-notif-mmn\data\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B0A7BB-ED02-459A-8BC9-90521C93D020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD98E62-5999-483C-BF19-682375E481DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="104">
   <si>
     <t>gender</t>
   </si>
@@ -59,9 +59,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>PN</t>
-  </si>
-  <si>
     <t>BT</t>
   </si>
   <si>
@@ -273,6 +270,87 @@
   </si>
   <si>
     <t>Indivisual  SN  ERP not good</t>
+  </si>
+  <si>
+    <t>bad electrode = None</t>
+  </si>
+  <si>
+    <t>No bad channel</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>SN_tone</t>
+  </si>
+  <si>
+    <t>Whoop_doop</t>
+  </si>
+  <si>
+    <t>droplet</t>
+  </si>
+  <si>
+    <t>realme</t>
+  </si>
+  <si>
+    <t>realme_fun</t>
+  </si>
+  <si>
+    <t>iphone_note</t>
+  </si>
+  <si>
+    <t>oneplustune</t>
+  </si>
+  <si>
+    <t>voyar</t>
+  </si>
+  <si>
+    <t>oneplus_meet</t>
+  </si>
+  <si>
+    <t>oneplus_blissful</t>
+  </si>
+  <si>
+    <t>encounter_vivo</t>
+  </si>
+  <si>
+    <t>vibration</t>
+  </si>
+  <si>
+    <t>oppo</t>
+  </si>
+  <si>
+    <t>oppo_joy</t>
+  </si>
+  <si>
+    <t>jai_shree_shyam</t>
+  </si>
+  <si>
+    <t>_andes_vivo</t>
+  </si>
+  <si>
+    <t>skyline_samsung</t>
+  </si>
+  <si>
+    <t>chime_moto</t>
+  </si>
+  <si>
+    <t>spaceline</t>
+  </si>
+  <si>
+    <t>Hello_inMoto</t>
+  </si>
+  <si>
+    <t>Tone_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT10 noisy channel  interpolated and further re reference </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP10 noisy channel  interpolated and further re reference </t>
+  </si>
+  <si>
+    <t>bad electrode = None Bad subject only very few epochs remains Discard as per recommended</t>
   </si>
 </sst>
 </file>
@@ -314,10 +392,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -653,8 +734,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865CEB74-C7CC-4BC7-8922-8A1352A31C27}">
-  <dimension ref="A1:I58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K58"/>
+  <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" style="1" customWidth="1"/>
@@ -664,19 +745,21 @@
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.5703125" style="1" customWidth="1"/>
     <col min="8" max="8" width="22.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="36" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -685,1436 +768,1805 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1">
         <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" s="1">
+        <v>8.6167800453514701E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1">
         <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K3" s="1">
+        <v>3.6575963718820798E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1">
         <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" s="1">
+        <v>8.6167800453514701E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1">
         <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K5" s="1">
+        <v>3.4829931972789101E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1">
         <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" s="1">
+        <v>6.7800453514739196E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1">
         <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="1">
+        <v>3.6575963718820798E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1">
         <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K8" s="1">
+        <v>6.4852607709750499E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1">
         <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="1">
+        <v>8.6167800453514701E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1">
         <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.92743764172335E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1">
         <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" s="1">
+        <v>3.1428571428571403E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1">
         <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K12" s="1">
+        <v>6.6893424036281101E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1">
         <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="1">
+        <v>6.7800453514739196E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1">
         <v>18</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="1">
+        <v>6.7800453514739196E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1">
         <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1.18367346938775E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1">
         <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K16" s="1">
+        <v>7.21088435374149E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1">
         <v>18</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K17" s="1">
+        <v>6.4852607709750499E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1">
         <v>21</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K18" s="1">
+        <v>3.1428571428571403E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1">
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1.92743764172335E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1">
         <v>21</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="1">
+        <v>9.3650793650793592E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1">
         <v>21</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K21" s="1">
+        <v>8.1405895691609893E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1">
         <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1.92743764172335E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1">
         <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K23" s="1">
+        <v>3.4829931972789101E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1">
         <v>34</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K24" s="1">
+        <v>3.1428571428571403E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0.197551020408163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="1">
         <v>28</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1.92743764172335E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1">
         <v>34</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27" s="1">
+        <v>3.6575963718820798E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="1">
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1.29251700680272E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1">
         <v>25</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K29" s="1">
+        <v>3.6575963718820798E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1">
         <v>34</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K30" s="1">
+        <v>7.1836734693877496E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1">
         <v>31</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K31" s="1">
+        <v>7.1836734693877496E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1">
         <v>34</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K32" s="1">
+        <v>6.7800453514739196E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="1">
         <v>38</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K33" s="1">
+        <v>8.1405895691609893E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B34" s="1">
         <v>28</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1.92743764172335E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35" s="1">
         <v>27</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K35" s="1">
+        <v>3.4829931972789101E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36" s="1">
         <v>25</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1.92743764172335E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B37" s="1">
         <v>23</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K37" s="1">
+        <v>6.4852607709750499E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B38" s="1">
         <v>26</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K38" s="1">
+        <v>6.4852607709750499E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B39" s="1">
         <v>22</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K39" s="1">
+        <v>8.6167800453514701E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B40" s="1">
         <v>22</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K40" s="1">
+        <v>1.18367346938775E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B41" s="1">
         <v>21</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0.197551020408163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B42" s="1">
         <v>23</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K42" s="1">
+        <v>3.6575963718820798E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B43" s="1">
         <v>24</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1.92743764172335E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B44" s="1">
         <v>23</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1.29251700680272E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" s="1">
         <v>23</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K45" s="1">
+        <v>6.4852607709750499E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46" s="1">
         <v>48</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K46" s="1">
+        <v>3.4829931972789101E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47" s="1">
         <v>24</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K47" s="1">
+        <v>8.6167800453514701E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B48" s="1">
         <v>20</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1.49206349206349E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" s="1">
         <v>26</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K49" s="1">
+        <v>9.7505668934240301E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B50" s="1">
         <v>20</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0.197551020408163</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B51" s="1">
         <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K51" s="1">
+        <v>2.9251700680272101E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" s="1">
         <v>22</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K52" s="1">
+        <v>8.6167800453514701E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B53" s="1">
         <v>21</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K53" s="1">
+        <v>1.29251700680272E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B54" s="1">
         <v>20</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K54" s="1">
+        <v>6.4852607709750499E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B55" s="1">
         <v>25</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K55" s="1">
+        <v>8.6167800453514701E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B56" s="1">
         <v>20</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K56" s="1">
+        <v>1.92743764172335E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B57" s="1">
         <v>23</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K57" s="1">
+        <v>1.00907029478458E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B58" s="1">
         <v>22</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K58" s="1">
+        <v>3.6575963718820798E-2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E52" xr:uid="{865CEB74-C7CC-4BC7-8922-8A1352A31C27}"/>
+  <autoFilter ref="A1:J58" xr:uid="{865CEB74-C7CC-4BC7-8922-8A1352A31C27}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Processed/Participant_details.xlsx
+++ b/data/Processed/Participant_details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ecf-exp2-notif-mmn\data\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD98E62-5999-483C-BF19-682375E481DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7664F962-A936-48AB-889F-EFC601272E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="123">
   <si>
     <t>gender</t>
   </si>
@@ -351,6 +351,63 @@
   </si>
   <si>
     <t>bad electrode = None Bad subject only very few epochs remains Discard as per recommended</t>
+  </si>
+  <si>
+    <t>bad electrode = FT9</t>
+  </si>
+  <si>
+    <t>bad electrode = F3</t>
+  </si>
+  <si>
+    <t>bad electrode =AF7</t>
+  </si>
+  <si>
+    <t>bad electrode =FT9, FC3</t>
+  </si>
+  <si>
+    <t>bad electrode =PO4</t>
+  </si>
+  <si>
+    <t>bad electrode =AF7, PO7, PO3</t>
+  </si>
+  <si>
+    <t>bad electrode = PO7</t>
+  </si>
+  <si>
+    <t>bad electrode = AFz, CP5</t>
+  </si>
+  <si>
+    <t>bad electrode = P7</t>
+  </si>
+  <si>
+    <t>bad electrode = FC3; Bad data , drop subject</t>
+  </si>
+  <si>
+    <t>bad electrode = P5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droped </t>
+  </si>
+  <si>
+    <t xml:space="preserve">bad electrode = FC3; it have additional S24 ,S25 trgger reponse </t>
+  </si>
+  <si>
+    <t>bad electrode = FT7</t>
+  </si>
+  <si>
+    <t>bad electrode = FC3</t>
+  </si>
+  <si>
+    <t>bad electrode = FC4</t>
+  </si>
+  <si>
+    <t>bad electrode = Afz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t>bad electrode = CP5, Fp2, C1</t>
   </si>
 </sst>
 </file>
@@ -734,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865CEB74-C7CC-4BC7-8922-8A1352A31C27}">
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="1" customWidth="1"/>
@@ -1084,9 +1141,6 @@
       <c r="G11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="J11" s="1" t="s">
         <v>86</v>
       </c>
@@ -1203,6 +1257,9 @@
       <c r="G15" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I15" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="J15" s="1" t="s">
         <v>88</v>
       </c>
@@ -1409,6 +1466,9 @@
       <c r="G22" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I22" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="J22" s="1" t="s">
         <v>85</v>
       </c>
@@ -1438,6 +1498,9 @@
       <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I23" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J23" s="1" t="s">
         <v>82</v>
       </c>
@@ -1470,6 +1533,9 @@
       <c r="H24" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="I24" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J24" s="1" t="s">
         <v>86</v>
       </c>
@@ -1531,6 +1597,9 @@
       <c r="H26" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I26" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J26" s="1" t="s">
         <v>85</v>
       </c>
@@ -1563,6 +1632,9 @@
       <c r="H27" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I27" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="J27" s="1" t="s">
         <v>81</v>
       </c>
@@ -1595,6 +1667,9 @@
       <c r="H28" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I28" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J28" s="1" t="s">
         <v>92</v>
       </c>
@@ -1627,6 +1702,9 @@
       <c r="H29" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I29" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J29" s="1" t="s">
         <v>81</v>
       </c>
@@ -1659,6 +1737,9 @@
       <c r="H30" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I30" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J30" s="1" t="s">
         <v>93</v>
       </c>
@@ -1691,6 +1772,9 @@
       <c r="H31" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I31" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="J31" s="1" t="s">
         <v>93</v>
       </c>
@@ -1723,6 +1807,9 @@
       <c r="H32" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I32" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J32" s="1" t="s">
         <v>84</v>
       </c>
@@ -1755,6 +1842,9 @@
       <c r="H33" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I33" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J33" s="1" t="s">
         <v>90</v>
       </c>
@@ -1819,6 +1909,9 @@
       <c r="H35" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I35" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="J35" s="1" t="s">
         <v>82</v>
       </c>
@@ -1851,6 +1944,9 @@
       <c r="H36" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I36" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="J36" s="1" t="s">
         <v>85</v>
       </c>
@@ -1883,6 +1979,9 @@
       <c r="H37" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I37" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="J37" s="1" t="s">
         <v>98</v>
       </c>
@@ -1915,6 +2014,9 @@
       <c r="H38" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I38" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="J38" s="1" t="s">
         <v>98</v>
       </c>
@@ -1947,6 +2049,9 @@
       <c r="H39" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I39" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="J39" s="1" t="s">
         <v>99</v>
       </c>
@@ -1979,6 +2084,9 @@
       <c r="H40" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I40" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J40" s="1" t="s">
         <v>88</v>
       </c>
@@ -2011,6 +2119,9 @@
       <c r="H41" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I41" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J41" s="1" t="s">
         <v>91</v>
       </c>
@@ -2043,6 +2154,9 @@
       <c r="H42" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I42" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J42" s="1" t="s">
         <v>81</v>
       </c>
@@ -2075,6 +2189,9 @@
       <c r="H43" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I43" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="J43" s="1" t="s">
         <v>85</v>
       </c>
@@ -2107,6 +2224,9 @@
       <c r="H44" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I44" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J44" s="1" t="s">
         <v>92</v>
       </c>
@@ -2139,6 +2259,9 @@
       <c r="H45" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I45" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="J45" s="1" t="s">
         <v>98</v>
       </c>
@@ -2171,6 +2294,9 @@
       <c r="H46" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I46" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="J46" s="1" t="s">
         <v>82</v>
       </c>
@@ -2203,6 +2329,9 @@
       <c r="H47" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I47" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J47" s="1" t="s">
         <v>99</v>
       </c>
@@ -2235,6 +2364,9 @@
       <c r="H48" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I48" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J48" s="1" t="s">
         <v>94</v>
       </c>
@@ -2242,7 +2374,7 @@
         <v>1.49206349206349E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>60</v>
       </c>
@@ -2267,6 +2399,9 @@
       <c r="H49" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I49" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="J49" s="1" t="s">
         <v>95</v>
       </c>
@@ -2274,7 +2409,7 @@
         <v>9.7505668934240301E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>61</v>
       </c>
@@ -2299,6 +2434,9 @@
       <c r="H50" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I50" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="J50" s="1" t="s">
         <v>91</v>
       </c>
@@ -2306,7 +2444,7 @@
         <v>0.197551020408163</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>62</v>
       </c>
@@ -2331,6 +2469,9 @@
       <c r="H51" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I51" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="J51" s="1" t="s">
         <v>96</v>
       </c>
@@ -2338,7 +2479,7 @@
         <v>2.9251700680272101E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>63</v>
       </c>
@@ -2363,6 +2504,9 @@
       <c r="H52" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I52" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="J52" s="1" t="s">
         <v>99</v>
       </c>
@@ -2370,7 +2514,7 @@
         <v>8.6167800453514701E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>64</v>
       </c>
@@ -2395,6 +2539,9 @@
       <c r="H53" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I53" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="J53" s="1" t="s">
         <v>92</v>
       </c>
@@ -2402,7 +2549,7 @@
         <v>1.29251700680272E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>65</v>
       </c>
@@ -2427,6 +2574,9 @@
       <c r="H54" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I54" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="J54" s="1" t="s">
         <v>98</v>
       </c>
@@ -2434,7 +2584,7 @@
         <v>6.4852607709750499E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>66</v>
       </c>
@@ -2459,6 +2609,9 @@
       <c r="H55" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I55" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="J55" s="1" t="s">
         <v>99</v>
       </c>
@@ -2466,7 +2619,7 @@
         <v>8.6167800453514701E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>67</v>
       </c>
@@ -2501,7 +2654,7 @@
         <v>1.92743764172335E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>68</v>
       </c>
@@ -2526,6 +2679,9 @@
       <c r="H57" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I57" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="J57" s="1" t="s">
         <v>97</v>
       </c>
@@ -2533,7 +2689,7 @@
         <v>1.00907029478458E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>69</v>
       </c>
@@ -2558,11 +2714,24 @@
       <c r="H58" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I58" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="J58" s="1" t="s">
         <v>81</v>
       </c>
       <c r="K58" s="1">
         <v>3.6575963718820798E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O60" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I63" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/Processed/Participant_details.xlsx
+++ b/data/Processed/Participant_details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ecf-exp2-notif-mmn\data\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7664F962-A936-48AB-889F-EFC601272E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B16392-DE4E-46D2-9DCE-69E40F0CDF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="124">
   <si>
     <t>gender</t>
   </si>
@@ -368,9 +368,6 @@
     <t>bad electrode =PO4</t>
   </si>
   <si>
-    <t>bad electrode =AF7, PO7, PO3</t>
-  </si>
-  <si>
     <t>bad electrode = PO7</t>
   </si>
   <si>
@@ -386,9 +383,6 @@
     <t>bad electrode = P5</t>
   </si>
   <si>
-    <t xml:space="preserve">Droped </t>
-  </si>
-  <si>
     <t xml:space="preserve">bad electrode = FC3; it have additional S24 ,S25 trgger reponse </t>
   </si>
   <si>
@@ -408,6 +402,15 @@
   </si>
   <si>
     <t>bad electrode = CP5, Fp2, C1</t>
+  </si>
+  <si>
+    <t>bad electrode = ['AF7', 'PO4', 'PO3', 'FT9', 'F2']</t>
+  </si>
+  <si>
+    <t>bad electrode =['AF7', 'Fp1', 'F6', 'AF8', 'FC3', 'PO3', 'TP7', 'P5', 'PO7']</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ['PO3', 'P6', 'F4', 'Oz', 'FT9'] Dropped </t>
   </si>
 </sst>
 </file>
@@ -1802,13 +1805,13 @@
         <v>79</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>84</v>
@@ -1980,7 +1983,7 @@
         <v>6</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>98</v>
@@ -2015,7 +2018,7 @@
         <v>6</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>98</v>
@@ -2050,7 +2053,7 @@
         <v>6</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>99</v>
@@ -2111,10 +2114,10 @@
         <v>3</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>6</v>
@@ -2190,7 +2193,7 @@
         <v>6</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>85</v>
@@ -2295,7 +2298,7 @@
         <v>6</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>82</v>
@@ -2400,7 +2403,7 @@
         <v>6</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>95</v>
@@ -2435,7 +2438,7 @@
         <v>6</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>91</v>
@@ -2505,7 +2508,7 @@
         <v>6</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>99</v>
@@ -2540,7 +2543,7 @@
         <v>6</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>92</v>
@@ -2575,7 +2578,7 @@
         <v>6</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>98</v>
@@ -2610,7 +2613,7 @@
         <v>6</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>99</v>
@@ -2680,7 +2683,7 @@
         <v>6</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>97</v>
@@ -2715,7 +2718,7 @@
         <v>6</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>81</v>
@@ -2726,7 +2729,7 @@
     </row>
     <row r="60" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O60" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/data/Processed/Participant_details.xlsx
+++ b/data/Processed/Participant_details.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ecf-exp2-notif-mmn\data\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B16392-DE4E-46D2-9DCE-69E40F0CDF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC46F4F-6BF6-4479-9E8A-272CE7B6B779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
+    <workbookView xWindow="31170" yWindow="0" windowWidth="29040" windowHeight="15840" xr2:uid="{96E66801-AEE8-4A11-9971-0DA162AB42F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="125">
   <si>
     <t>gender</t>
   </si>
@@ -383,9 +383,6 @@
     <t>bad electrode = P5</t>
   </si>
   <si>
-    <t xml:space="preserve">bad electrode = FC3; it have additional S24 ,S25 trgger reponse </t>
-  </si>
-  <si>
     <t>bad electrode = FT7</t>
   </si>
   <si>
@@ -404,20 +401,86 @@
     <t>bad electrode = CP5, Fp2, C1</t>
   </si>
   <si>
-    <t>bad electrode = ['AF7', 'PO4', 'PO3', 'FT9', 'F2']</t>
-  </si>
-  <si>
-    <t>bad electrode =['AF7', 'Fp1', 'F6', 'AF8', 'FC3', 'PO3', 'TP7', 'P5', 'PO7']</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ['PO3', 'P6', 'F4', 'Oz', 'FT9'] Dropped </t>
+    <t>bad electrode = FC3; it have additional S24 ,S25 trgger reponse ; further don't have psycho data to shift as system stopped before saving the results</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">bad electrode =['AF7', 'Fp1', 'F6', 'AF8', 'FC3', 'PO3', 'TP7', 'P5', 'PO7'];  The EEG trigger for the Control block is 21, 22, 23, 24, and 25, whereas for PS as the standard tone has stimulus markers with 31, 32, 33, 34, and 35. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Corrected</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bad electrode = ['AF7', 'PO4', 'PO3', 'FT9', 'F2'] ; Control Block EEG is collected at  the end with trigger value similar to personlized tone as EEG recoring was not resumed in actual place.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Corrected</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">bad electrode = None; Each block of data is collected by interchanging the tone in first block so need not to shift movie to sound trigger.  </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> ['P5', 'P6','F5',  'Oz', 'FT9'] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dropped ; lot of noise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ;The recording system closed after two blocks. The third block (beep tone as deviant ) is recorded in a separate file SD058_B3.eeg. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Raw data corrected </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -431,13 +494,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -452,12 +535,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1810,8 +1899,8 @@
       <c r="H32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>121</v>
+      <c r="I32" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>84</v>
@@ -1982,8 +2071,8 @@
       <c r="H37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>122</v>
+      <c r="I37" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>98</v>
@@ -2367,8 +2456,8 @@
       <c r="H48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>77</v>
+      <c r="I48" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>94</v>
@@ -2402,8 +2491,8 @@
       <c r="H49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I49" s="2" t="s">
-        <v>123</v>
+      <c r="I49" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>95</v>
@@ -2479,7 +2568,7 @@
         <v>96</v>
       </c>
       <c r="K51" s="1">
-        <v>2.9251700680272101E-3</v>
+        <v>2.9251699999999999E-3</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2507,8 +2596,8 @@
       <c r="H52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>114</v>
+      <c r="I52" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>99</v>
@@ -2543,7 +2632,7 @@
         <v>6</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>92</v>
@@ -2578,7 +2667,7 @@
         <v>6</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>98</v>
@@ -2613,7 +2702,7 @@
         <v>6</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>99</v>
@@ -2683,7 +2772,7 @@
         <v>6</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>97</v>
@@ -2718,7 +2807,7 @@
         <v>6</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>81</v>
@@ -2729,7 +2818,7 @@
     </row>
     <row r="60" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O60" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
